--- a/assets/raw-data/biospecimen/test_bioproben.xlsx
+++ b/assets/raw-data/biospecimen/test_bioproben.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HesseE\mex-extractors\assets\raw-data\biospecimen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esinsj\code\mex-extractors\assets\raw-data\biospecimen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354591A6-9D06-4C48-9836-C1B4890CFD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E3FE32-FC4B-451E-889E-81330E2C3334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,19 @@
     <sheet name="Probe1" sheetId="1" r:id="rId1"/>
     <sheet name="Probe2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -26,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="88">
   <si>
     <t>Probensammlung</t>
   </si>
@@ -286,7 +297,10 @@
     <t>testverwandedoi2</t>
   </si>
   <si>
-    <t>C1</t>
+    <t>PRNT</t>
+  </si>
+  <si>
+    <t>PARENT Dept.</t>
   </si>
 </sst>
 </file>
@@ -585,7 +599,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">

--- a/assets/raw-data/biospecimen/test_bioproben.xlsx
+++ b/assets/raw-data/biospecimen/test_bioproben.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esinsj\code\mex-extractors\assets\raw-data\biospecimen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E3FE32-FC4B-451E-889E-81330E2C3334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A5547A-24BA-4ACD-8C57-420EBBB25500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="86">
   <si>
     <t>Probensammlung</t>
   </si>
@@ -81,6 +81,9 @@
     <t>verantwortliche Fachabteilung</t>
   </si>
   <si>
+    <t>PARENT Dept.</t>
+  </si>
+  <si>
     <t>mitwirkende Fachabteilung</t>
   </si>
   <si>
@@ -171,9 +174,6 @@
     <t>Vorhandene Anzahl der Proben</t>
   </si>
   <si>
-    <t>Testanzahl</t>
-  </si>
-  <si>
     <t>Rechte</t>
   </si>
   <si>
@@ -231,6 +231,9 @@
     <t>felicitasj@rki.de</t>
   </si>
   <si>
+    <t>PRNT</t>
+  </si>
+  <si>
     <t xml:space="preserve">mitwirkende Testabteilung2                                                                                                      </t>
   </si>
   <si>
@@ -276,9 +279,6 @@
     <t>Testtool2</t>
   </si>
   <si>
-    <t>Testanzahl2</t>
-  </si>
-  <si>
     <t>Testrechte2</t>
   </si>
   <si>
@@ -295,12 +295,6 @@
   </si>
   <si>
     <t>testverwandedoi2</t>
-  </si>
-  <si>
-    <t>PRNT</t>
-  </si>
-  <si>
-    <t>PARENT Dept.</t>
   </si>
 </sst>
 </file>
@@ -599,175 +593,175 @@
         <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="1" t="s">
         <v>44</v>
+      </c>
+      <c r="B32" s="1">
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -902,175 +896,175 @@
         <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>79</v>
+        <v>44</v>
+      </c>
+      <c r="B32" s="1">
+        <v>999</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
